--- a/www/ig/fhir/core/StructureDefinition-fr-core-healthcare-service.xlsx
+++ b/www/ig/fhir/core/StructureDefinition-fr-core-healthcare-service.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T10:06:33+02:00</t>
+    <t>2026-03-19T12:11:47+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,10 +69,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org/)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(work))</t>
+    <t>Interop'Santé (http://interopsante.org)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -84,8 +84,8 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Profile of the HealthcareService resource for France. This profile adds the element serviceTypeDuration to associate the service with the duration of this service. 
-Profil de la ressource HealthcareService pour l'usage en France. Ce profil ajoute l'élément serviceTypeDuration de façon à associer le service avec la durée du service.</t>
+    <t>Profile of the HealthcareService resource for France. This profile adds the element serviceTypeDuration to associate the service with the duration of this service. This profile needs to be revised, in particular to ensure consistency with the ROR project (https://interop.esante.gouv.fr/ig/fhir/ror).
+Profil de la ressource HealthcareService pour l'usage en France. Ce profil ajoute l'élément serviceTypeDuration de façon à associer le service avec la durée du service. Ce profil doit être retravaillé, pour être notamment mis en cohérence avec le projet ROR (https://interop.esante.gouv.fr/ig/fhir/ror).</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -115,7 +115,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/HealthcareService</t>
+    <t>http://hl7.org/fhir/StructureDefinition/HealthcareService|4.0.1</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -415,7 +415,7 @@
     <t>Identifies where the resource comes from</t>
   </si>
   <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
   </si>
   <si>
     <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
@@ -428,14 +428,14 @@
     <t>HealthcareService.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
     <t>Profiles this resource claims to conform to</t>
   </si>
   <si>
-    <t>A list of profiles (references to [StructureDefinition](structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](structuredefinition-definitions.html#StructureDefinition.url).</t>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
   </si>
   <si>
     <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
@@ -457,6 +457,9 @@
     <t>fr-canonical</t>
   </si>
   <si>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-healthcare-service|2.2.0</t>
+  </si>
+  <si>
     <t>HealthcareService.meta.security</t>
   </si>
   <si>
@@ -479,7 +482,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -503,7 +506,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -546,7 +549,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -622,14 +625,16 @@
     <t>serviceTypeDuration</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-service-type-duration}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-service-type-duration|2.2.0}
 </t>
   </si>
   <si>
     <t>FR Core Service Type Duration Extension</t>
   </si>
   <si>
-    <t>This French extension allows to associate the type of service with the duration of this service | Cette extension française permet d'associer le type de service avec la durée de ce service.</t>
+    <t>Cette extension française permet d'associer le type de service avec la durée de ce service.
++This French extension allows to associate the type of service with the duration of this service</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -695,7 +700,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-use</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
   </si>
   <si>
     <t>Identifier.use</t>
@@ -726,7 +731,7 @@
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -799,7 +804,7 @@
     <t>HealthcareService.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -846,7 +851,7 @@
     <t>HealthcareService.providedBy</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0)
 </t>
   </si>
   <si>
@@ -881,7 +886,7 @@
     <t>A category of the service(s) that could be provided.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/service-category</t>
+    <t>http://hl7.org/fhir/ValueSet/service-category|4.0.1</t>
   </si>
   <si>
     <t>.code</t>
@@ -906,7 +911,7 @@
     <t>Additional details about where the content was created (e.g. clinical specialty).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/service-type</t>
+    <t>http://hl7.org/fhir/ValueSet/service-type|4.0.1</t>
   </si>
   <si>
     <t>.actrelationship[typeCode=COMP.act[classCode=ACT][moodCode=DEF].code</t>
@@ -921,13 +926,13 @@
     <t>Collection of specialties handled by the service site. This is more of a medical term.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-practitioner-specialty</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-practitioner-specialty|2.2.0</t>
   </si>
   <si>
     <t>HealthcareService.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-location)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-location|2.2.0)
 </t>
   </si>
   <si>
@@ -1005,24 +1010,20 @@
     <t>HealthcareService.telecom</t>
   </si>
   <si>
-    <t xml:space="preserve">ContactPoint {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point}
+    <t xml:space="preserve">ContactPoint {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point|2.2.0}
 </t>
   </si>
   <si>
-    <t>Details of a Technology mediated contact point (phone, fax, email, etc.)</t>
-  </si>
-  <si>
-    <t>Details for all kinds of technology mediated contact points for a person or organization, including telephone, email, etc.</t>
+    <t>Contacts related to the healthcare service</t>
+  </si>
+  <si>
+    <t>List of contacts related to this specific healthcare service.</t>
   </si>
   <si>
     <t>If this is empty, then refer to the location's contacts.</t>
   </si>
   <si>
-    <t>cpt-2:A system is required if a value is provided. {value.empty() or system.exists()}
-ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
-  </si>
-  <si>
-    <t>TEL</t>
+    <t>.telecom</t>
   </si>
   <si>
     <t>HealthcareService.coverageArea</t>
@@ -1052,7 +1053,7 @@
     <t>The provision means being commissioned by, contractually obliged or financially sourced. Types of costings that may apply to this healthcare service, such if the service may be available for free, some discounts available, or fees apply.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/service-provision-conditions</t>
+    <t>http://hl7.org/fhir/ValueSet/service-provision-conditions|4.0.1</t>
   </si>
   <si>
     <t>.actrelationship[typeCode=PRCN].observation[moodCode=EVN.CRT]</t>
@@ -1136,7 +1137,7 @@
     <t>Government or local programs that this service applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/program</t>
+    <t>http://hl7.org/fhir/ValueSet/program|4.0.1</t>
   </si>
   <si>
     <t>.actrelationship[typeCode=PERT].observation</t>
@@ -1181,7 +1182,7 @@
     <t>The methods of referral can be used when referring to a specific HealthCareService resource.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/service-referral-method</t>
+    <t>http://hl7.org/fhir/ValueSet/service-referral-method|4.0.1</t>
   </si>
   <si>
     <t>HealthcareService.appointmentRequired</t>
@@ -1314,7 +1315,7 @@
     <t>HealthcareService.endpoint</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Endpoint)
+    <t xml:space="preserve">Reference(Endpoint|4.0.1)
 </t>
   </si>
   <si>
@@ -1634,17 +1635,17 @@
   <dimension ref="A1:AL69"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="46.328125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="46.328125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="19.234375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="38.4609375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.1484375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.58203125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.94140625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="14.7109375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="12.1875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="39.96484375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="39.96484375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="16.59375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="33.17578125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.30078125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="3.953125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.265625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="80.69140625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="74.19921875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1653,24 +1654,24 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="38.1875" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="15.77734375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="16.13671875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="17.40234375" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.9609375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="95.3984375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="63.453125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.8828125" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="20.84375" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="40.0859375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="15.703125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="13.125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="46.328125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.53125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.890625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="32.94140625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="13.609375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="13.91796875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="82.29296875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="59.328125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="34.578125" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="13.54296875" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="11.3203125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="39.96484375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="8.22265625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="8.53125" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="99.8984375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="33.05078125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="86.17578125" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="28.5078125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2805,7 +2806,7 @@
         <v>76</v>
       </c>
       <c r="S11" t="s" s="2">
-        <v>3</v>
+        <v>142</v>
       </c>
       <c r="T11" t="s" s="2">
         <v>76</v>
@@ -2867,10 +2868,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2893,16 +2894,16 @@
         <v>86</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -2928,13 +2929,13 @@
         <v>76</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>76</v>
@@ -2952,7 +2953,7 @@
         <v>76</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>77</v>
@@ -2975,10 +2976,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3001,16 +3002,16 @@
         <v>86</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3036,13 +3037,13 @@
         <v>76</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>76</v>
@@ -3060,7 +3061,7 @@
         <v>76</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>77</v>
@@ -3083,10 +3084,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3112,13 +3113,13 @@
         <v>127</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3168,7 +3169,7 @@
         <v>76</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
@@ -3191,10 +3192,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3217,16 +3218,16 @@
         <v>76</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3252,13 +3253,13 @@
         <v>76</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>76</v>
@@ -3276,7 +3277,7 @@
         <v>76</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
@@ -3299,14 +3300,14 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3325,16 +3326,16 @@
         <v>76</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3384,7 +3385,7 @@
         <v>76</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
@@ -3399,7 +3400,7 @@
         <v>97</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>76</v>
@@ -3407,14 +3408,14 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3433,16 +3434,16 @@
         <v>76</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3492,7 +3493,7 @@
         <v>76</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
@@ -3507,7 +3508,7 @@
         <v>76</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>76</v>
@@ -3515,10 +3516,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3544,10 +3545,10 @@
         <v>106</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3596,7 +3597,7 @@
         <v>112</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
@@ -3619,13 +3620,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>76</v>
@@ -3647,13 +3648,13 @@
         <v>76</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3704,7 +3705,7 @@
         <v>76</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
@@ -3713,7 +3714,7 @@
         <v>78</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>114</v>
@@ -3727,10 +3728,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3756,16 +3757,16 @@
         <v>106</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N20" t="s" s="2">
         <v>109</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>76</v>
@@ -3814,7 +3815,7 @@
         <v>76</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -3829,7 +3830,7 @@
         <v>114</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>76</v>
@@ -3837,10 +3838,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3863,13 +3864,13 @@
         <v>86</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3920,7 +3921,7 @@
         <v>76</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
@@ -3935,18 +3936,18 @@
         <v>97</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4049,10 +4050,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4157,10 +4158,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4183,19 +4184,19 @@
         <v>86</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>76</v>
@@ -4220,11 +4221,11 @@
         <v>76</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>76</v>
@@ -4242,7 +4243,7 @@
         <v>76</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -4257,7 +4258,7 @@
         <v>97</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>76</v>
@@ -4265,10 +4266,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4291,19 +4292,19 @@
         <v>86</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>76</v>
@@ -4328,13 +4329,13 @@
         <v>76</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>76</v>
@@ -4352,7 +4353,7 @@
         <v>76</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
@@ -4367,7 +4368,7 @@
         <v>97</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>76</v>
@@ -4375,10 +4376,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4404,16 +4405,16 @@
         <v>127</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>76</v>
@@ -4426,7 +4427,7 @@
         <v>76</v>
       </c>
       <c r="T26" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="U26" t="s" s="2">
         <v>76</v>
@@ -4462,7 +4463,7 @@
         <v>76</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
@@ -4477,7 +4478,7 @@
         <v>97</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>76</v>
@@ -4485,10 +4486,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4514,13 +4515,13 @@
         <v>99</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4534,7 +4535,7 @@
         <v>76</v>
       </c>
       <c r="T27" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="U27" t="s" s="2">
         <v>76</v>
@@ -4570,7 +4571,7 @@
         <v>76</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
@@ -4585,7 +4586,7 @@
         <v>97</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>76</v>
@@ -4593,10 +4594,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4619,13 +4620,13 @@
         <v>86</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4676,7 +4677,7 @@
         <v>76</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
@@ -4691,7 +4692,7 @@
         <v>97</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>76</v>
@@ -4699,10 +4700,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4725,16 +4726,16 @@
         <v>86</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4784,7 +4785,7 @@
         <v>76</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
@@ -4799,7 +4800,7 @@
         <v>97</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>76</v>
@@ -4807,10 +4808,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4833,23 +4834,23 @@
         <v>86</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q30" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="R30" t="s" s="2">
         <v>76</v>
@@ -4894,7 +4895,7 @@
         <v>76</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
@@ -4909,18 +4910,18 @@
         <v>97</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4943,16 +4944,16 @@
         <v>86</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5002,7 +5003,7 @@
         <v>76</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
@@ -5017,7 +5018,7 @@
         <v>97</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>76</v>
@@ -5025,14 +5026,14 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5051,16 +5052,16 @@
         <v>86</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5086,13 +5087,13 @@
         <v>76</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>76</v>
@@ -5110,7 +5111,7 @@
         <v>76</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
@@ -5125,22 +5126,22 @@
         <v>97</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5159,13 +5160,13 @@
         <v>86</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5192,13 +5193,13 @@
         <v>76</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>76</v>
@@ -5216,7 +5217,7 @@
         <v>76</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -5231,7 +5232,7 @@
         <v>97</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>76</v>
@@ -5239,10 +5240,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5265,13 +5266,13 @@
         <v>86</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5298,11 +5299,11 @@
         <v>76</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Y34" s="2"/>
       <c r="Z34" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>76</v>
@@ -5320,7 +5321,7 @@
         <v>76</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
@@ -5335,7 +5336,7 @@
         <v>97</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>76</v>
@@ -5343,10 +5344,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5369,13 +5370,13 @@
         <v>86</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5426,7 +5427,7 @@
         <v>76</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
@@ -5441,18 +5442,18 @@
         <v>97</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5478,10 +5479,10 @@
         <v>99</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5532,7 +5533,7 @@
         <v>76</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
@@ -5547,7 +5548,7 @@
         <v>97</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>76</v>
@@ -5555,10 +5556,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5584,13 +5585,13 @@
         <v>99</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5640,7 +5641,7 @@
         <v>76</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
@@ -5655,7 +5656,7 @@
         <v>97</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>76</v>
@@ -5663,10 +5664,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5689,13 +5690,13 @@
         <v>76</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5746,7 +5747,7 @@
         <v>76</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
@@ -5761,7 +5762,7 @@
         <v>97</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>76</v>
@@ -5769,10 +5770,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5795,13 +5796,13 @@
         <v>86</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5852,7 +5853,7 @@
         <v>76</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
@@ -5867,7 +5868,7 @@
         <v>97</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>76</v>
@@ -5875,10 +5876,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5901,16 +5902,16 @@
         <v>76</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -5960,7 +5961,7 @@
         <v>76</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
@@ -5969,10 +5970,10 @@
         <v>78</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>198</v>
+        <v>76</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>322</v>
+        <v>97</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>323</v>
@@ -6009,7 +6010,7 @@
         <v>76</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L41" t="s" s="2">
         <v>325</v>
@@ -6117,7 +6118,7 @@
         <v>76</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L42" t="s" s="2">
         <v>330</v>
@@ -6152,7 +6153,7 @@
         <v>76</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Y42" t="s" s="2">
         <v>331</v>
@@ -6557,7 +6558,7 @@
         <v>109</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>76</v>
@@ -6621,7 +6622,7 @@
         <v>114</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>76</v>
@@ -6655,7 +6656,7 @@
         <v>76</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L47" t="s" s="2">
         <v>347</v>
@@ -6688,7 +6689,7 @@
         <v>76</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Y47" t="s" s="2">
         <v>349</v>
@@ -6761,7 +6762,7 @@
         <v>76</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L48" t="s" s="2">
         <v>351</v>
@@ -6869,7 +6870,7 @@
         <v>76</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L49" t="s" s="2">
         <v>356</v>
@@ -6904,7 +6905,7 @@
         <v>76</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Y49" t="s" s="2">
         <v>359</v>
@@ -6977,7 +6978,7 @@
         <v>76</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L50" t="s" s="2">
         <v>363</v>
@@ -7012,7 +7013,7 @@
         <v>76</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Y50" t="s" s="2">
         <v>366</v>
@@ -7085,7 +7086,7 @@
         <v>76</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L51" t="s" s="2">
         <v>368</v>
@@ -7120,13 +7121,13 @@
         <v>76</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>76</v>
@@ -7193,7 +7194,7 @@
         <v>76</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L52" t="s" s="2">
         <v>372</v>
@@ -7226,7 +7227,7 @@
         <v>76</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Y52" t="s" s="2">
         <v>374</v>
@@ -7299,7 +7300,7 @@
         <v>76</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L53" t="s" s="2">
         <v>377</v>
@@ -7739,7 +7740,7 @@
         <v>109</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>76</v>
@@ -7803,7 +7804,7 @@
         <v>114</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>76</v>
@@ -7837,7 +7838,7 @@
         <v>76</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L58" t="s" s="2">
         <v>388</v>
@@ -7870,7 +7871,7 @@
         <v>76</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Y58" t="s" s="2">
         <v>390</v>
@@ -7943,7 +7944,7 @@
         <v>76</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L59" t="s" s="2">
         <v>393</v>
@@ -8597,7 +8598,7 @@
         <v>109</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>76</v>
@@ -8661,7 +8662,7 @@
         <v>114</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>76</v>
@@ -8801,7 +8802,7 @@
         <v>76</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L67" t="s" s="2">
         <v>413</v>

--- a/www/ig/fhir/core/StructureDefinition-fr-core-healthcare-service.xlsx
+++ b/www/ig/fhir/core/StructureDefinition-fr-core-healthcare-service.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0</t>
+    <t>2.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T12:11:47+01:00</t>
+    <t>2024-09-04T10:06:33+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,10 +69,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(Work))</t>
+    <t>Interop'Santé (http://interopsante.org/)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -84,8 +84,8 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Profile of the HealthcareService resource for France. This profile adds the element serviceTypeDuration to associate the service with the duration of this service. This profile needs to be revised, in particular to ensure consistency with the ROR project (https://interop.esante.gouv.fr/ig/fhir/ror).
-Profil de la ressource HealthcareService pour l'usage en France. Ce profil ajoute l'élément serviceTypeDuration de façon à associer le service avec la durée du service. Ce profil doit être retravaillé, pour être notamment mis en cohérence avec le projet ROR (https://interop.esante.gouv.fr/ig/fhir/ror).</t>
+    <t>Profile of the HealthcareService resource for France. This profile adds the element serviceTypeDuration to associate the service with the duration of this service. 
+Profil de la ressource HealthcareService pour l'usage en France. Ce profil ajoute l'élément serviceTypeDuration de façon à associer le service avec la durée du service.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -115,7 +115,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/HealthcareService|4.0.1</t>
+    <t>http://hl7.org/fhir/StructureDefinition/HealthcareService</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -415,7 +415,7 @@
     <t>Identifies where the resource comes from</t>
   </si>
   <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
   </si>
   <si>
     <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
@@ -428,14 +428,14 @@
     <t>HealthcareService.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
+    <t xml:space="preserve">canonical(StructureDefinition)
 </t>
   </si>
   <si>
     <t>Profiles this resource claims to conform to</t>
   </si>
   <si>
-    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
+    <t>A list of profiles (references to [StructureDefinition](structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](structuredefinition-definitions.html#StructureDefinition.url).</t>
   </si>
   <si>
     <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
@@ -457,9 +457,6 @@
     <t>fr-canonical</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-healthcare-service|2.2.0</t>
-  </si>
-  <si>
     <t>HealthcareService.meta.security</t>
   </si>
   <si>
@@ -482,7 +479,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -506,7 +503,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -549,7 +546,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -625,16 +622,14 @@
     <t>serviceTypeDuration</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-service-type-duration|2.2.0}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-service-type-duration}
 </t>
   </si>
   <si>
     <t>FR Core Service Type Duration Extension</t>
   </si>
   <si>
-    <t>Cette extension française permet d'associer le type de service avec la durée de ce service.
--This French extension allows to associate the type of service with the duration of this service</t>
+    <t>This French extension allows to associate the type of service with the duration of this service | Cette extension française permet d'associer le type de service avec la durée de ce service.</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -700,7 +695,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-use</t>
   </si>
   <si>
     <t>Identifier.use</t>
@@ -731,7 +726,7 @@
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -804,7 +799,7 @@
     <t>HealthcareService.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization|4.0.1)
+    <t xml:space="preserve">Reference(Organization)
 </t>
   </si>
   <si>
@@ -851,7 +846,7 @@
     <t>HealthcareService.providedBy</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
 </t>
   </si>
   <si>
@@ -886,7 +881,7 @@
     <t>A category of the service(s) that could be provided.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/service-category|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/service-category</t>
   </si>
   <si>
     <t>.code</t>
@@ -911,7 +906,7 @@
     <t>Additional details about where the content was created (e.g. clinical specialty).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/service-type|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/service-type</t>
   </si>
   <si>
     <t>.actrelationship[typeCode=COMP.act[classCode=ACT][moodCode=DEF].code</t>
@@ -926,13 +921,13 @@
     <t>Collection of specialties handled by the service site. This is more of a medical term.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-practitioner-specialty|2.2.0</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-practitioner-specialty</t>
   </si>
   <si>
     <t>HealthcareService.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-location|2.2.0)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-location)
 </t>
   </si>
   <si>
@@ -1010,20 +1005,24 @@
     <t>HealthcareService.telecom</t>
   </si>
   <si>
-    <t xml:space="preserve">ContactPoint {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point|2.2.0}
+    <t xml:space="preserve">ContactPoint {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point}
 </t>
   </si>
   <si>
-    <t>Contacts related to the healthcare service</t>
-  </si>
-  <si>
-    <t>List of contacts related to this specific healthcare service.</t>
+    <t>Details of a Technology mediated contact point (phone, fax, email, etc.)</t>
+  </si>
+  <si>
+    <t>Details for all kinds of technology mediated contact points for a person or organization, including telephone, email, etc.</t>
   </si>
   <si>
     <t>If this is empty, then refer to the location's contacts.</t>
   </si>
   <si>
-    <t>.telecom</t>
+    <t>cpt-2:A system is required if a value is provided. {value.empty() or system.exists()}
+ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
+  </si>
+  <si>
+    <t>TEL</t>
   </si>
   <si>
     <t>HealthcareService.coverageArea</t>
@@ -1053,7 +1052,7 @@
     <t>The provision means being commissioned by, contractually obliged or financially sourced. Types of costings that may apply to this healthcare service, such if the service may be available for free, some discounts available, or fees apply.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/service-provision-conditions|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/service-provision-conditions</t>
   </si>
   <si>
     <t>.actrelationship[typeCode=PRCN].observation[moodCode=EVN.CRT]</t>
@@ -1137,7 +1136,7 @@
     <t>Government or local programs that this service applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/program|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/program</t>
   </si>
   <si>
     <t>.actrelationship[typeCode=PERT].observation</t>
@@ -1182,7 +1181,7 @@
     <t>The methods of referral can be used when referring to a specific HealthCareService resource.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/service-referral-method|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/service-referral-method</t>
   </si>
   <si>
     <t>HealthcareService.appointmentRequired</t>
@@ -1315,7 +1314,7 @@
     <t>HealthcareService.endpoint</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Endpoint|4.0.1)
+    <t xml:space="preserve">Reference(Endpoint)
 </t>
   </si>
   <si>
@@ -1635,17 +1634,17 @@
   <dimension ref="A1:AL69"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="39.96484375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="39.96484375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="16.59375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="33.17578125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.30078125" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="3.953125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.265625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="46.328125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="46.328125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="19.234375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="38.4609375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="6.1484375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.58203125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.94140625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="14.7109375" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="12.1875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="74.19921875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="80.69140625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1654,24 +1653,24 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="32.94140625" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="13.609375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="13.91796875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="82.29296875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="59.328125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="34.578125" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="13.54296875" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="11.3203125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="39.96484375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="8.22265625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="8.53125" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="38.1875" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="15.77734375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="16.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="17.40234375" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.9609375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="95.3984375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="63.453125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.8828125" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="20.84375" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="40.0859375" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="15.703125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="13.125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="46.328125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.53125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.890625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="86.17578125" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="28.5078125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="99.8984375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="33.05078125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2806,7 +2805,7 @@
         <v>76</v>
       </c>
       <c r="S11" t="s" s="2">
-        <v>142</v>
+        <v>3</v>
       </c>
       <c r="T11" t="s" s="2">
         <v>76</v>
@@ -2868,10 +2867,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2894,16 +2893,16 @@
         <v>86</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>144</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
         <v>145</v>
       </c>
-      <c r="M12" t="s" s="2">
+      <c r="N12" t="s" s="2">
         <v>146</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>147</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -2929,31 +2928,31 @@
         <v>76</v>
       </c>
       <c r="X12" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="Y12" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="Y12" t="s" s="2">
+      <c r="Z12" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="Z12" t="s" s="2">
+      <c r="AA12" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB12" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC12" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD12" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE12" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF12" t="s" s="2">
         <v>150</v>
-      </c>
-      <c r="AA12" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB12" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC12" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD12" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE12" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF12" t="s" s="2">
-        <v>151</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>77</v>
@@ -2976,10 +2975,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3002,16 +3001,16 @@
         <v>86</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L13" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="M13" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>155</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3037,31 +3036,31 @@
         <v>76</v>
       </c>
       <c r="X13" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="Y13" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="Y13" t="s" s="2">
+      <c r="Z13" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="Z13" t="s" s="2">
+      <c r="AA13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF13" t="s" s="2">
         <v>158</v>
-      </c>
-      <c r="AA13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>159</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>77</v>
@@ -3084,10 +3083,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3113,13 +3112,13 @@
         <v>127</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3169,7 +3168,7 @@
         <v>76</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
@@ -3192,10 +3191,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3218,16 +3217,16 @@
         <v>76</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="M15" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>168</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>169</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3253,31 +3252,31 @@
         <v>76</v>
       </c>
       <c r="X15" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="Y15" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="Y15" t="s" s="2">
+      <c r="Z15" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="Z15" t="s" s="2">
+      <c r="AA15" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF15" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
@@ -3300,14 +3299,14 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3326,16 +3325,16 @@
         <v>76</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>178</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>179</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3385,7 +3384,7 @@
         <v>76</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
@@ -3400,7 +3399,7 @@
         <v>97</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>76</v>
@@ -3408,14 +3407,14 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3434,16 +3433,16 @@
         <v>76</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>187</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3493,7 +3492,7 @@
         <v>76</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
@@ -3508,7 +3507,7 @@
         <v>76</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>76</v>
@@ -3516,10 +3515,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3545,10 +3544,10 @@
         <v>106</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>191</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>192</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3597,7 +3596,7 @@
         <v>112</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
@@ -3620,13 +3619,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="C19" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="C19" t="s" s="2">
-        <v>195</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>76</v>
@@ -3648,13 +3647,13 @@
         <v>76</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>197</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>198</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3705,7 +3704,7 @@
         <v>76</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
@@ -3714,7 +3713,7 @@
         <v>78</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>114</v>
@@ -3728,10 +3727,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3757,16 +3756,16 @@
         <v>106</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>202</v>
       </c>
       <c r="N20" t="s" s="2">
         <v>109</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>76</v>
@@ -3815,7 +3814,7 @@
         <v>76</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -3830,7 +3829,7 @@
         <v>114</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>76</v>
@@ -3838,10 +3837,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3864,13 +3863,13 @@
         <v>86</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3921,7 +3920,7 @@
         <v>76</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
@@ -3936,18 +3935,18 @@
         <v>97</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="AL21" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="AL21" t="s" s="2">
-        <v>210</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4050,10 +4049,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4158,10 +4157,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4184,19 +4183,19 @@
         <v>86</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="N24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>76</v>
@@ -4221,29 +4220,29 @@
         <v>76</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="AA24" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB24" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF24" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="AA24" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB24" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC24" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD24" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE24" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF24" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -4258,7 +4257,7 @@
         <v>97</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>76</v>
@@ -4266,10 +4265,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4292,19 +4291,19 @@
         <v>86</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="N25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>227</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>76</v>
@@ -4329,31 +4328,31 @@
         <v>76</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="Y25" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="Z25" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="Z25" t="s" s="2">
+      <c r="AA25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF25" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="AA25" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
@@ -4368,7 +4367,7 @@
         <v>97</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>76</v>
@@ -4376,10 +4375,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4405,16 +4404,16 @@
         <v>127</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="N26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>235</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>76</v>
@@ -4427,43 +4426,43 @@
         <v>76</v>
       </c>
       <c r="T26" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="U26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF26" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="U26" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V26" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W26" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X26" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y26" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z26" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA26" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB26" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD26" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE26" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF26" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
@@ -4478,7 +4477,7 @@
         <v>97</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>76</v>
@@ -4486,10 +4485,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4515,13 +4514,13 @@
         <v>99</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4535,43 +4534,43 @@
         <v>76</v>
       </c>
       <c r="T27" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X27" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z27" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF27" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="U27" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V27" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W27" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X27" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z27" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA27" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB27" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF27" t="s" s="2">
-        <v>244</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
@@ -4586,7 +4585,7 @@
         <v>97</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>76</v>
@@ -4594,10 +4593,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4620,13 +4619,13 @@
         <v>86</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>249</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4677,7 +4676,7 @@
         <v>76</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
@@ -4692,7 +4691,7 @@
         <v>97</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>76</v>
@@ -4700,10 +4699,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4726,16 +4725,16 @@
         <v>86</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>256</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4785,7 +4784,7 @@
         <v>76</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
@@ -4800,7 +4799,7 @@
         <v>97</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>76</v>
@@ -4808,10 +4807,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4834,23 +4833,23 @@
         <v>86</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="M30" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q30" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="R30" t="s" s="2">
         <v>76</v>
@@ -4895,7 +4894,7 @@
         <v>76</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
@@ -4910,18 +4909,18 @@
         <v>97</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AL30" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="AL30" t="s" s="2">
-        <v>266</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4944,16 +4943,16 @@
         <v>86</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>271</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5003,7 +5002,7 @@
         <v>76</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
@@ -5018,7 +5017,7 @@
         <v>97</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>76</v>
@@ -5026,14 +5025,14 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5052,16 +5051,16 @@
         <v>86</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>277</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5087,14 +5086,14 @@
         <v>76</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="Y32" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="Z32" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="Z32" t="s" s="2">
-        <v>279</v>
-      </c>
       <c r="AA32" t="s" s="2">
         <v>76</v>
       </c>
@@ -5111,7 +5110,7 @@
         <v>76</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
@@ -5126,22 +5125,22 @@
         <v>97</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AL32" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="AL32" t="s" s="2">
-        <v>281</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5160,13 +5159,13 @@
         <v>86</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>285</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5193,14 +5192,14 @@
         <v>76</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="Y33" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="Z33" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="Z33" t="s" s="2">
-        <v>287</v>
-      </c>
       <c r="AA33" t="s" s="2">
         <v>76</v>
       </c>
@@ -5217,7 +5216,7 @@
         <v>76</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -5232,7 +5231,7 @@
         <v>97</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>76</v>
@@ -5240,10 +5239,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5266,13 +5265,13 @@
         <v>86</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>290</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>291</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5299,11 +5298,11 @@
         <v>76</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="Y34" s="2"/>
       <c r="Z34" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>76</v>
@@ -5321,7 +5320,7 @@
         <v>76</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
@@ -5336,7 +5335,7 @@
         <v>97</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>76</v>
@@ -5344,10 +5343,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5370,13 +5369,13 @@
         <v>86</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>296</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5427,7 +5426,7 @@
         <v>76</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
@@ -5442,18 +5441,18 @@
         <v>97</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AL35" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="AL35" t="s" s="2">
-        <v>298</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5479,10 +5478,10 @@
         <v>99</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>301</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5533,7 +5532,7 @@
         <v>76</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
@@ -5548,7 +5547,7 @@
         <v>97</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>76</v>
@@ -5556,10 +5555,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5585,13 +5584,13 @@
         <v>99</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>306</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5641,7 +5640,7 @@
         <v>76</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
@@ -5656,7 +5655,7 @@
         <v>97</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>76</v>
@@ -5664,10 +5663,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5690,13 +5689,13 @@
         <v>76</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>311</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5747,7 +5746,7 @@
         <v>76</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
@@ -5762,7 +5761,7 @@
         <v>97</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>76</v>
@@ -5770,10 +5769,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5796,13 +5795,13 @@
         <v>86</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>316</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5853,7 +5852,7 @@
         <v>76</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
@@ -5868,7 +5867,7 @@
         <v>97</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>76</v>
@@ -5876,10 +5875,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5902,16 +5901,16 @@
         <v>76</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -5961,7 +5960,7 @@
         <v>76</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
@@ -5970,10 +5969,10 @@
         <v>78</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>76</v>
+        <v>198</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>97</v>
+        <v>322</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>323</v>
@@ -6010,7 +6009,7 @@
         <v>76</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="L41" t="s" s="2">
         <v>325</v>
@@ -6118,7 +6117,7 @@
         <v>76</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="L42" t="s" s="2">
         <v>330</v>
@@ -6153,7 +6152,7 @@
         <v>76</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="Y42" t="s" s="2">
         <v>331</v>
@@ -6558,7 +6557,7 @@
         <v>109</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>76</v>
@@ -6622,7 +6621,7 @@
         <v>114</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>76</v>
@@ -6656,7 +6655,7 @@
         <v>76</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="L47" t="s" s="2">
         <v>347</v>
@@ -6689,7 +6688,7 @@
         <v>76</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="Y47" t="s" s="2">
         <v>349</v>
@@ -6762,7 +6761,7 @@
         <v>76</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="L48" t="s" s="2">
         <v>351</v>
@@ -6870,7 +6869,7 @@
         <v>76</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="L49" t="s" s="2">
         <v>356</v>
@@ -6905,7 +6904,7 @@
         <v>76</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="Y49" t="s" s="2">
         <v>359</v>
@@ -6978,7 +6977,7 @@
         <v>76</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="L50" t="s" s="2">
         <v>363</v>
@@ -7013,7 +7012,7 @@
         <v>76</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="Y50" t="s" s="2">
         <v>366</v>
@@ -7086,7 +7085,7 @@
         <v>76</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="L51" t="s" s="2">
         <v>368</v>
@@ -7121,13 +7120,13 @@
         <v>76</v>
       </c>
       <c r="X51" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="Y51" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="Y51" t="s" s="2">
+      <c r="Z51" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="Z51" t="s" s="2">
-        <v>172</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>76</v>
@@ -7194,7 +7193,7 @@
         <v>76</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="L52" t="s" s="2">
         <v>372</v>
@@ -7227,7 +7226,7 @@
         <v>76</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="Y52" t="s" s="2">
         <v>374</v>
@@ -7300,7 +7299,7 @@
         <v>76</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="L53" t="s" s="2">
         <v>377</v>
@@ -7740,7 +7739,7 @@
         <v>109</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>76</v>
@@ -7804,7 +7803,7 @@
         <v>114</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>76</v>
@@ -7838,7 +7837,7 @@
         <v>76</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="L58" t="s" s="2">
         <v>388</v>
@@ -7871,7 +7870,7 @@
         <v>76</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Y58" t="s" s="2">
         <v>390</v>
@@ -7944,7 +7943,7 @@
         <v>76</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="L59" t="s" s="2">
         <v>393</v>
@@ -8598,7 +8597,7 @@
         <v>109</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>76</v>
@@ -8662,7 +8661,7 @@
         <v>114</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>76</v>
@@ -8802,7 +8801,7 @@
         <v>76</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="L67" t="s" s="2">
         <v>413</v>

--- a/www/ig/fhir/core/StructureDefinition-fr-core-healthcare-service.xlsx
+++ b/www/ig/fhir/core/StructureDefinition-fr-core-healthcare-service.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T10:06:33+02:00</t>
+    <t>2026-03-25T18:08:32+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,10 +69,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org/)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(work))</t>
+    <t>Interop'Santé (http://interopsante.org)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -84,8 +84,8 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Profile of the HealthcareService resource for France. This profile adds the element serviceTypeDuration to associate the service with the duration of this service. 
-Profil de la ressource HealthcareService pour l'usage en France. Ce profil ajoute l'élément serviceTypeDuration de façon à associer le service avec la durée du service.</t>
+    <t>Profile of the HealthcareService resource for France. This profile adds the element serviceTypeDuration to associate the service with the duration of this service. This profile needs to be revised, in particular to ensure consistency with the ROR project (https://interop.esante.gouv.fr/ig/fhir/ror).
+Profil de la ressource HealthcareService pour l'usage en France. Ce profil ajoute l'élément serviceTypeDuration de façon à associer le service avec la durée du service. Ce profil doit être retravaillé, pour être notamment mis en cohérence avec le projet ROR (https://interop.esante.gouv.fr/ig/fhir/ror).</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -115,7 +115,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/HealthcareService</t>
+    <t>http://hl7.org/fhir/StructureDefinition/HealthcareService|4.0.1</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -415,7 +415,7 @@
     <t>Identifies where the resource comes from</t>
   </si>
   <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
   </si>
   <si>
     <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
@@ -428,14 +428,14 @@
     <t>HealthcareService.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
     <t>Profiles this resource claims to conform to</t>
   </si>
   <si>
-    <t>A list of profiles (references to [StructureDefinition](structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](structuredefinition-definitions.html#StructureDefinition.url).</t>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
   </si>
   <si>
     <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
@@ -457,6 +457,9 @@
     <t>fr-canonical</t>
   </si>
   <si>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-healthcare-service|2.2.0</t>
+  </si>
+  <si>
     <t>HealthcareService.meta.security</t>
   </si>
   <si>
@@ -479,7 +482,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -503,7 +506,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -546,7 +549,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -622,14 +625,16 @@
     <t>serviceTypeDuration</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-service-type-duration}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-service-type-duration|2.2.0}
 </t>
   </si>
   <si>
     <t>FR Core Service Type Duration Extension</t>
   </si>
   <si>
-    <t>This French extension allows to associate the type of service with the duration of this service | Cette extension française permet d'associer le type de service avec la durée de ce service.</t>
+    <t>Cette extension française permet d'associer le type de service avec la durée de ce service.
++This French extension allows to associate the type of service with the duration of this service</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -695,7 +700,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-use</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
   </si>
   <si>
     <t>Identifier.use</t>
@@ -726,7 +731,7 @@
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -799,7 +804,7 @@
     <t>HealthcareService.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -846,7 +851,7 @@
     <t>HealthcareService.providedBy</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0)
 </t>
   </si>
   <si>
@@ -881,7 +886,7 @@
     <t>A category of the service(s) that could be provided.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/service-category</t>
+    <t>http://hl7.org/fhir/ValueSet/service-category|4.0.1</t>
   </si>
   <si>
     <t>.code</t>
@@ -906,7 +911,7 @@
     <t>Additional details about where the content was created (e.g. clinical specialty).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/service-type</t>
+    <t>http://hl7.org/fhir/ValueSet/service-type|4.0.1</t>
   </si>
   <si>
     <t>.actrelationship[typeCode=COMP.act[classCode=ACT][moodCode=DEF].code</t>
@@ -921,13 +926,13 @@
     <t>Collection of specialties handled by the service site. This is more of a medical term.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-practitioner-specialty</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-practitioner-specialty|2.2.0</t>
   </si>
   <si>
     <t>HealthcareService.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-location)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-location|2.2.0)
 </t>
   </si>
   <si>
@@ -1005,24 +1010,20 @@
     <t>HealthcareService.telecom</t>
   </si>
   <si>
-    <t xml:space="preserve">ContactPoint {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point}
+    <t xml:space="preserve">ContactPoint {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point|2.2.0}
 </t>
   </si>
   <si>
-    <t>Details of a Technology mediated contact point (phone, fax, email, etc.)</t>
-  </si>
-  <si>
-    <t>Details for all kinds of technology mediated contact points for a person or organization, including telephone, email, etc.</t>
+    <t>Contacts related to the healthcare service</t>
+  </si>
+  <si>
+    <t>List of contacts related to this specific healthcare service.</t>
   </si>
   <si>
     <t>If this is empty, then refer to the location's contacts.</t>
   </si>
   <si>
-    <t>cpt-2:A system is required if a value is provided. {value.empty() or system.exists()}
-ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
-  </si>
-  <si>
-    <t>TEL</t>
+    <t>.telecom</t>
   </si>
   <si>
     <t>HealthcareService.coverageArea</t>
@@ -1052,7 +1053,7 @@
     <t>The provision means being commissioned by, contractually obliged or financially sourced. Types of costings that may apply to this healthcare service, such if the service may be available for free, some discounts available, or fees apply.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/service-provision-conditions</t>
+    <t>http://hl7.org/fhir/ValueSet/service-provision-conditions|4.0.1</t>
   </si>
   <si>
     <t>.actrelationship[typeCode=PRCN].observation[moodCode=EVN.CRT]</t>
@@ -1136,7 +1137,7 @@
     <t>Government or local programs that this service applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/program</t>
+    <t>http://hl7.org/fhir/ValueSet/program|4.0.1</t>
   </si>
   <si>
     <t>.actrelationship[typeCode=PERT].observation</t>
@@ -1181,7 +1182,7 @@
     <t>The methods of referral can be used when referring to a specific HealthCareService resource.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/service-referral-method</t>
+    <t>http://hl7.org/fhir/ValueSet/service-referral-method|4.0.1</t>
   </si>
   <si>
     <t>HealthcareService.appointmentRequired</t>
@@ -1314,7 +1315,7 @@
     <t>HealthcareService.endpoint</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Endpoint)
+    <t xml:space="preserve">Reference(Endpoint|4.0.1)
 </t>
   </si>
   <si>
@@ -1634,17 +1635,17 @@
   <dimension ref="A1:AL69"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="46.328125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="46.328125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="19.234375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="38.4609375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.1484375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.58203125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.94140625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="14.7109375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="12.1875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="39.96484375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="39.96484375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="16.59375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="33.17578125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.30078125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="3.953125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.265625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="80.69140625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="74.19921875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1653,24 +1654,24 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="38.1875" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="15.77734375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="16.13671875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="17.40234375" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.9609375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="95.3984375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="63.453125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.8828125" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="20.84375" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="40.0859375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="15.703125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="13.125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="46.328125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.53125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.890625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="32.94140625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="13.609375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="13.91796875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="82.29296875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="59.328125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="34.578125" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="13.54296875" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="11.3203125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="39.96484375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="8.22265625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="8.53125" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="99.8984375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="33.05078125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="86.17578125" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="28.5078125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2805,7 +2806,7 @@
         <v>76</v>
       </c>
       <c r="S11" t="s" s="2">
-        <v>3</v>
+        <v>142</v>
       </c>
       <c r="T11" t="s" s="2">
         <v>76</v>
@@ -2867,10 +2868,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2893,16 +2894,16 @@
         <v>86</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -2928,13 +2929,13 @@
         <v>76</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>76</v>
@@ -2952,7 +2953,7 @@
         <v>76</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>77</v>
@@ -2975,10 +2976,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3001,16 +3002,16 @@
         <v>86</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3036,13 +3037,13 @@
         <v>76</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>76</v>
@@ -3060,7 +3061,7 @@
         <v>76</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>77</v>
@@ -3083,10 +3084,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3112,13 +3113,13 @@
         <v>127</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3168,7 +3169,7 @@
         <v>76</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
@@ -3191,10 +3192,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3217,16 +3218,16 @@
         <v>76</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3252,13 +3253,13 @@
         <v>76</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>76</v>
@@ -3276,7 +3277,7 @@
         <v>76</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
@@ -3299,14 +3300,14 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3325,16 +3326,16 @@
         <v>76</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3384,7 +3385,7 @@
         <v>76</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
@@ -3399,7 +3400,7 @@
         <v>97</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>76</v>
@@ -3407,14 +3408,14 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3433,16 +3434,16 @@
         <v>76</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3492,7 +3493,7 @@
         <v>76</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
@@ -3507,7 +3508,7 @@
         <v>76</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>76</v>
@@ -3515,10 +3516,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3544,10 +3545,10 @@
         <v>106</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3596,7 +3597,7 @@
         <v>112</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
@@ -3619,13 +3620,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>76</v>
@@ -3647,13 +3648,13 @@
         <v>76</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3704,7 +3705,7 @@
         <v>76</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
@@ -3713,7 +3714,7 @@
         <v>78</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>114</v>
@@ -3727,10 +3728,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3756,16 +3757,16 @@
         <v>106</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N20" t="s" s="2">
         <v>109</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>76</v>
@@ -3814,7 +3815,7 @@
         <v>76</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -3829,7 +3830,7 @@
         <v>114</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>76</v>
@@ -3837,10 +3838,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3863,13 +3864,13 @@
         <v>86</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3920,7 +3921,7 @@
         <v>76</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
@@ -3935,18 +3936,18 @@
         <v>97</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4049,10 +4050,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4157,10 +4158,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4183,19 +4184,19 @@
         <v>86</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>76</v>
@@ -4220,11 +4221,11 @@
         <v>76</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>76</v>
@@ -4242,7 +4243,7 @@
         <v>76</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -4257,7 +4258,7 @@
         <v>97</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>76</v>
@@ -4265,10 +4266,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4291,19 +4292,19 @@
         <v>86</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>76</v>
@@ -4328,13 +4329,13 @@
         <v>76</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>76</v>
@@ -4352,7 +4353,7 @@
         <v>76</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
@@ -4367,7 +4368,7 @@
         <v>97</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>76</v>
@@ -4375,10 +4376,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4404,16 +4405,16 @@
         <v>127</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>76</v>
@@ -4426,7 +4427,7 @@
         <v>76</v>
       </c>
       <c r="T26" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="U26" t="s" s="2">
         <v>76</v>
@@ -4462,7 +4463,7 @@
         <v>76</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
@@ -4477,7 +4478,7 @@
         <v>97</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>76</v>
@@ -4485,10 +4486,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4514,13 +4515,13 @@
         <v>99</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4534,7 +4535,7 @@
         <v>76</v>
       </c>
       <c r="T27" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="U27" t="s" s="2">
         <v>76</v>
@@ -4570,7 +4571,7 @@
         <v>76</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
@@ -4585,7 +4586,7 @@
         <v>97</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>76</v>
@@ -4593,10 +4594,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4619,13 +4620,13 @@
         <v>86</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4676,7 +4677,7 @@
         <v>76</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
@@ -4691,7 +4692,7 @@
         <v>97</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>76</v>
@@ -4699,10 +4700,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4725,16 +4726,16 @@
         <v>86</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4784,7 +4785,7 @@
         <v>76</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
@@ -4799,7 +4800,7 @@
         <v>97</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>76</v>
@@ -4807,10 +4808,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4833,23 +4834,23 @@
         <v>86</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q30" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="R30" t="s" s="2">
         <v>76</v>
@@ -4894,7 +4895,7 @@
         <v>76</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
@@ -4909,18 +4910,18 @@
         <v>97</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4943,16 +4944,16 @@
         <v>86</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5002,7 +5003,7 @@
         <v>76</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
@@ -5017,7 +5018,7 @@
         <v>97</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>76</v>
@@ -5025,14 +5026,14 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5051,16 +5052,16 @@
         <v>86</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5086,13 +5087,13 @@
         <v>76</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>76</v>
@@ -5110,7 +5111,7 @@
         <v>76</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
@@ -5125,22 +5126,22 @@
         <v>97</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5159,13 +5160,13 @@
         <v>86</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5192,13 +5193,13 @@
         <v>76</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>76</v>
@@ -5216,7 +5217,7 @@
         <v>76</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -5231,7 +5232,7 @@
         <v>97</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>76</v>
@@ -5239,10 +5240,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5265,13 +5266,13 @@
         <v>86</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5298,11 +5299,11 @@
         <v>76</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Y34" s="2"/>
       <c r="Z34" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>76</v>
@@ -5320,7 +5321,7 @@
         <v>76</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
@@ -5335,7 +5336,7 @@
         <v>97</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>76</v>
@@ -5343,10 +5344,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5369,13 +5370,13 @@
         <v>86</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5426,7 +5427,7 @@
         <v>76</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
@@ -5441,18 +5442,18 @@
         <v>97</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5478,10 +5479,10 @@
         <v>99</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5532,7 +5533,7 @@
         <v>76</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
@@ -5547,7 +5548,7 @@
         <v>97</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>76</v>
@@ -5555,10 +5556,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5584,13 +5585,13 @@
         <v>99</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5640,7 +5641,7 @@
         <v>76</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
@@ -5655,7 +5656,7 @@
         <v>97</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>76</v>
@@ -5663,10 +5664,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5689,13 +5690,13 @@
         <v>76</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5746,7 +5747,7 @@
         <v>76</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
@@ -5761,7 +5762,7 @@
         <v>97</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>76</v>
@@ -5769,10 +5770,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5795,13 +5796,13 @@
         <v>86</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5852,7 +5853,7 @@
         <v>76</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
@@ -5867,7 +5868,7 @@
         <v>97</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>76</v>
@@ -5875,10 +5876,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5901,16 +5902,16 @@
         <v>76</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -5960,7 +5961,7 @@
         <v>76</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
@@ -5969,10 +5970,10 @@
         <v>78</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>198</v>
+        <v>76</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>322</v>
+        <v>97</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>323</v>
@@ -6009,7 +6010,7 @@
         <v>76</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L41" t="s" s="2">
         <v>325</v>
@@ -6117,7 +6118,7 @@
         <v>76</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L42" t="s" s="2">
         <v>330</v>
@@ -6152,7 +6153,7 @@
         <v>76</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Y42" t="s" s="2">
         <v>331</v>
@@ -6557,7 +6558,7 @@
         <v>109</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>76</v>
@@ -6621,7 +6622,7 @@
         <v>114</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>76</v>
@@ -6655,7 +6656,7 @@
         <v>76</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L47" t="s" s="2">
         <v>347</v>
@@ -6688,7 +6689,7 @@
         <v>76</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Y47" t="s" s="2">
         <v>349</v>
@@ -6761,7 +6762,7 @@
         <v>76</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L48" t="s" s="2">
         <v>351</v>
@@ -6869,7 +6870,7 @@
         <v>76</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L49" t="s" s="2">
         <v>356</v>
@@ -6904,7 +6905,7 @@
         <v>76</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Y49" t="s" s="2">
         <v>359</v>
@@ -6977,7 +6978,7 @@
         <v>76</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L50" t="s" s="2">
         <v>363</v>
@@ -7012,7 +7013,7 @@
         <v>76</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Y50" t="s" s="2">
         <v>366</v>
@@ -7085,7 +7086,7 @@
         <v>76</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L51" t="s" s="2">
         <v>368</v>
@@ -7120,13 +7121,13 @@
         <v>76</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>76</v>
@@ -7193,7 +7194,7 @@
         <v>76</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L52" t="s" s="2">
         <v>372</v>
@@ -7226,7 +7227,7 @@
         <v>76</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Y52" t="s" s="2">
         <v>374</v>
@@ -7299,7 +7300,7 @@
         <v>76</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L53" t="s" s="2">
         <v>377</v>
@@ -7739,7 +7740,7 @@
         <v>109</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>76</v>
@@ -7803,7 +7804,7 @@
         <v>114</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>76</v>
@@ -7837,7 +7838,7 @@
         <v>76</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L58" t="s" s="2">
         <v>388</v>
@@ -7870,7 +7871,7 @@
         <v>76</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Y58" t="s" s="2">
         <v>390</v>
@@ -7943,7 +7944,7 @@
         <v>76</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L59" t="s" s="2">
         <v>393</v>
@@ -8597,7 +8598,7 @@
         <v>109</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>76</v>
@@ -8661,7 +8662,7 @@
         <v>114</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>76</v>
@@ -8801,7 +8802,7 @@
         <v>76</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L67" t="s" s="2">
         <v>413</v>
